--- a/outputs/57117.xlsx
+++ b/outputs/57117.xlsx
@@ -181,20 +181,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -390,142 +394,142 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="F2" s="3" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("BA",D2)),"BA",IF(ISNUMBER(SEARCH("MA",D2)),"MA",""))</f>
         <v>BA</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="2" t="str">
+      <c r="F3" s="3" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("BA",D3)),"BA",IF(ISNUMBER(SEARCH("MA",D3)),"MA",""))</f>
         <v>BA</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="F4" s="2" t="str">
+      <c r="F4" s="3" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("BA",D4)),"BA",IF(ISNUMBER(SEARCH("MA",D4)),"MA",""))</f>
         <v>MA</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="2" t="str">
+      <c r="F5" s="3" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH("BA",D5)),"BA",IF(ISNUMBER(SEARCH("MA",D5)),"MA",""))</f>
         <v>MA</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>18</v>
       </c>
     </row>

--- a/outputs/57117.xlsx
+++ b/outputs/57117.xlsx
@@ -442,7 +442,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("BA",D2)),"BA",IF(ISNUMBER(SEARCH("MA",D2)),"MA",""))</f>
+        <f aca="false">LEFT(D2,2)</f>
         <v>BA</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -469,7 +469,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("BA",D3)),"BA",IF(ISNUMBER(SEARCH("MA",D3)),"MA",""))</f>
+        <f aca="false">LEFT(D3,2)</f>
         <v>BA</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("BA",D4)),"BA",IF(ISNUMBER(SEARCH("MA",D4)),"MA",""))</f>
+        <f aca="false">LEFT(D4,2)</f>
         <v>MA</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -523,7 +523,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(SEARCH("BA",D5)),"BA",IF(ISNUMBER(SEARCH("MA",D5)),"MA",""))</f>
+        <f aca="false">LEFT(D5,2)</f>
         <v>MA</v>
       </c>
       <c r="G5" s="4" t="s">
